--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7813,0.0380,0.0260,0.1279</t>
-  </si>
-  <si>
-    <t>0.1126,0.0031,0.0087,0.9450</t>
-  </si>
-  <si>
-    <t>0.8366,0.0110,0.0042,0.1258</t>
-  </si>
-  <si>
-    <t>0.0136,0.0028,0.0026,0.9920</t>
-  </si>
-  <si>
-    <t>0.9911,0.0024,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9889,0.0107,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9718,0.0083,0.0070,0.0046</t>
-  </si>
-  <si>
-    <t>0.9830,0.0087,0.0027,0.0016</t>
-  </si>
-  <si>
-    <t>0.9807,0.0095,0.0009,0.0024</t>
-  </si>
-  <si>
-    <t>0.9895,0.0036,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9774,0.0187,0.0086,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0016,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.7062,0.0188,0.3209,0.0210</t>
-  </si>
-  <si>
-    <t>0.2925,0.0397,0.7506,0.0138</t>
-  </si>
-  <si>
-    <t>0.2945,0.0137,0.7948,0.0028</t>
-  </si>
-  <si>
-    <t>0.2085,0.0699,0.6678,0.0070</t>
-  </si>
-  <si>
-    <t>0.7634,0.0775,0.1870,0.0076</t>
-  </si>
-  <si>
-    <t>0.0049,0.9896,0.0012,0.0011</t>
-  </si>
-  <si>
-    <t>0.0058,0.9873,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.6383,0.5073,0.0072,0.0038</t>
-  </si>
-  <si>
-    <t>0.1549,0.8848,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.0051,0.9901,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.4084,0.0290,0.6186,0.0141</t>
-  </si>
-  <si>
-    <t>0.4205,0.0344,0.5938,0.0383</t>
-  </si>
-  <si>
-    <t>0.0016,0.0036,0.9836,0.0140</t>
-  </si>
-  <si>
-    <t>0.0421,0.0042,0.9564,0.0023</t>
-  </si>
-  <si>
-    <t>0.0300,0.0032,0.9627,0.0100</t>
-  </si>
-  <si>
-    <t>0.0250,0.0236,0.8806,0.0983</t>
-  </si>
-  <si>
-    <t>0.0069,0.0020,0.9930,0.0003</t>
-  </si>
-  <si>
-    <t>0.5354,0.6341,0.0013,0.0028</t>
-  </si>
-  <si>
-    <t>0.4963,0.4108,0.1570,0.0191</t>
-  </si>
-  <si>
-    <t>0.0052,0.0238,0.9761,0.0086</t>
-  </si>
-  <si>
-    <t>0.0377,0.7965,0.2465,0.0045</t>
-  </si>
-  <si>
-    <t>0.7666,0.0414,0.1960,0.0337</t>
-  </si>
-  <si>
-    <t>0.6197,0.3805,0.0562,0.0053</t>
-  </si>
-  <si>
-    <t>0.6553,0.4807,0.0087,0.0023</t>
-  </si>
-  <si>
-    <t>0.0024,0.9923,0.0080,0.0004</t>
-  </si>
-  <si>
-    <t>0.0124,0.7512,0.5669,0.0106</t>
-  </si>
-  <si>
-    <t>0.1068,0.1361,0.8687,0.0104</t>
-  </si>
-  <si>
-    <t>0.0721,0.0611,0.6170,0.2926</t>
-  </si>
-  <si>
-    <t>0.0274,0.0286,0.8448,0.1428</t>
-  </si>
-  <si>
-    <t>0.0070,0.1566,0.9500,0.0007</t>
-  </si>
-  <si>
-    <t>0.0218,0.8904,0.1525,0.0011</t>
-  </si>
-  <si>
-    <t>0.0106,0.2580,0.8958,0.0169</t>
-  </si>
-  <si>
-    <t>0.0370,0.3835,0.0253,0.9094</t>
-  </si>
-  <si>
-    <t>0.0047,0.9673,0.0254,0.0587</t>
-  </si>
-  <si>
-    <t>0.0034,0.9761,0.1707,0.0011</t>
-  </si>
-  <si>
-    <t>0.0112,0.9677,0.1131,0.0048</t>
-  </si>
-  <si>
-    <t>0.0019,0.2357,0.9780,0.0016</t>
-  </si>
-  <si>
-    <t>0.0010,0.1394,0.9909,0.0005</t>
-  </si>
-  <si>
-    <t>0.0767,0.0088,0.9184,0.0092</t>
-  </si>
-  <si>
-    <t>0.0174,0.0012,0.9689,0.0101</t>
-  </si>
-  <si>
-    <t>0.0009,0.0115,0.9915,0.0027</t>
-  </si>
-  <si>
-    <t>0.0039,0.0124,0.9875,0.0018</t>
-  </si>
-  <si>
-    <t>0.7989,0.2420,0.0191,0.0074</t>
-  </si>
-  <si>
-    <t>0.9732,0.0206,0.0067,0.0008</t>
-  </si>
-  <si>
-    <t>0.9439,0.0567,0.0062,0.0042</t>
-  </si>
-  <si>
-    <t>0.0012,0.0093,0.9929,0.0033</t>
-  </si>
-  <si>
-    <t>0.9712,0.0161,0.0012,0.0026</t>
-  </si>
-  <si>
-    <t>0.9872,0.0098,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9189,0.0663,0.0012,0.0062</t>
-  </si>
-  <si>
-    <t>0.0064,0.5507,0.9451,0.0016</t>
-  </si>
-  <si>
-    <t>0.0030,0.0673,0.9840,0.0030</t>
-  </si>
-  <si>
-    <t>0.0119,0.3234,0.9105,0.0041</t>
-  </si>
-  <si>
-    <t>0.0001,0.8235,0.9927,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0067,0.9901,0.0046</t>
-  </si>
-  <si>
-    <t>0.0203,0.8923,0.1170,0.0005</t>
-  </si>
-  <si>
-    <t>0.0343,0.9652,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9074,0.0487,0.0154,0.0055</t>
-  </si>
-  <si>
-    <t>0.7299,0.0461,0.2806,0.0187</t>
-  </si>
-  <si>
-    <t>0.0058,0.0080,0.9877,0.0016</t>
-  </si>
-  <si>
-    <t>0.0018,0.8565,0.7236,0.0002</t>
-  </si>
-  <si>
-    <t>0.0163,0.5521,0.8583,0.0025</t>
-  </si>
-  <si>
-    <t>0.0022,0.9814,0.1052,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.8966,0.9389,0.0001</t>
-  </si>
-  <si>
-    <t>0.0125,0.0019,0.1602,0.9455</t>
-  </si>
-  <si>
-    <t>0.0023,0.0020,0.0005,0.9984</t>
-  </si>
-  <si>
-    <t>0.0035,0.0015,0.0025,0.9968</t>
-  </si>
-  <si>
-    <t>0.0085,0.0005,0.0180,0.9869</t>
-  </si>
-  <si>
-    <t>0.0340,0.0060,0.0113,0.9787</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0020,0.9981</t>
-  </si>
-  <si>
-    <t>0.0009,0.9559,0.8042,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.8280,0.9544,0.0005</t>
-  </si>
-  <si>
-    <t>0.0089,0.5434,0.6704,0.0014</t>
-  </si>
-  <si>
-    <t>0.0039,0.5222,0.9152,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.9788,0.3144,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.7030,0.8797,0.0007</t>
-  </si>
-  <si>
-    <t>0.9827,0.0070,0.0021,0.0027</t>
-  </si>
-  <si>
-    <t>0.9193,0.0791,0.0173,0.0015</t>
-  </si>
-  <si>
-    <t>0.9775,0.0175,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9510,0.0388,0.0067,0.0039</t>
-  </si>
-  <si>
-    <t>0.9752,0.0169,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.9942,0.0018,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9703,0.0263,0.0077,0.0006</t>
-  </si>
-  <si>
-    <t>0.9738,0.0237,0.0039,0.0015</t>
-  </si>
-  <si>
-    <t>0.9910,0.0050,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9934,0.0021,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9948,0.0029,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0008,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9851,0.0158,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9918,0.0079,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9890,0.0075,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9970,0.0019</t>
-  </si>
-  <si>
-    <t>0.2349,0.0153,0.8128,0.0096</t>
-  </si>
-  <si>
-    <t>0.5512,0.0087,0.3809,0.0655</t>
-  </si>
-  <si>
-    <t>0.0730,0.0371,0.8975,0.0092</t>
-  </si>
-  <si>
-    <t>0.0172,0.9710,0.0045,0.0010</t>
-  </si>
-  <si>
-    <t>0.1744,0.8600,0.0063,0.0019</t>
-  </si>
-  <si>
-    <t>0.0239,0.9651,0.0009,0.0023</t>
-  </si>
-  <si>
-    <t>0.1238,0.8926,0.0016,0.0022</t>
-  </si>
-  <si>
-    <t>0.0590,0.9300,0.0026,0.0037</t>
-  </si>
-  <si>
-    <t>0.0109,0.9755,0.0071,0.0009</t>
-  </si>
-  <si>
-    <t>0.5069,0.6310,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.5721,0.0746,0.3305,0.0892</t>
-  </si>
-  <si>
-    <t>0.4523,0.0236,0.6229,0.0291</t>
-  </si>
-  <si>
-    <t>0.4852,0.2618,0.2362,0.0452</t>
-  </si>
-  <si>
-    <t>0.2436,0.1089,0.6675,0.0124</t>
-  </si>
-  <si>
-    <t>0.0184,0.3955,0.0238,0.9369</t>
-  </si>
-  <si>
-    <t>0.0015,0.9926,0.0121,0.0010</t>
-  </si>
-  <si>
-    <t>0.0018,0.9896,0.0075,0.0056</t>
-  </si>
-  <si>
-    <t>0.0387,0.9009,0.0363,0.0706</t>
-  </si>
-  <si>
-    <t>0.0001,0.9692,0.9296,0.0001</t>
-  </si>
-  <si>
-    <t>0.0098,0.9835,0.0047,0.0005</t>
-  </si>
-  <si>
-    <t>0.8153,0.3481,0.0030,0.0006</t>
-  </si>
-  <si>
-    <t>0.5589,0.5293,0.0082,0.0089</t>
-  </si>
-  <si>
-    <t>0.9875,0.0116,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.9531,0.0400,0.0078,0.0030</t>
-  </si>
-  <si>
-    <t>0.9654,0.0059,0.0045,0.0123</t>
-  </si>
-  <si>
-    <t>0.9710,0.0190,0.0084,0.0016</t>
-  </si>
-  <si>
-    <t>0.9922,0.0023,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9776,0.0139,0.0117,0.0008</t>
-  </si>
-  <si>
-    <t>0.9617,0.0202,0.0099,0.0036</t>
-  </si>
-  <si>
-    <t>0.9906,0.0063,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.0030,0.7185,0.9276,0.0010</t>
-  </si>
-  <si>
-    <t>0.0033,0.8952,0.6639,0.0003</t>
-  </si>
-  <si>
-    <t>0.0046,0.0410,0.9773,0.0017</t>
-  </si>
-  <si>
-    <t>0.0613,0.2001,0.7868,0.0056</t>
-  </si>
-  <si>
-    <t>0.5940,0.0044,0.2473,0.0759</t>
-  </si>
-  <si>
-    <t>0.7470,0.0574,0.1021,0.0356</t>
-  </si>
-  <si>
-    <t>0.3312,0.0037,0.8329,0.0025</t>
-  </si>
-  <si>
-    <t>0.6744,0.0640,0.3034,0.0147</t>
-  </si>
-  <si>
-    <t>0.0130,0.0013,0.0008,0.9949</t>
-  </si>
-  <si>
-    <t>0.0006,0.0024,0.0082,0.9979</t>
-  </si>
-  <si>
-    <t>0.0037,0.0178,0.0016,0.9961</t>
-  </si>
-  <si>
-    <t>0.0253,0.0008,0.0011,0.9907</t>
-  </si>
-  <si>
-    <t>0.0011,0.4742,0.9733,0.0002</t>
-  </si>
-  <si>
-    <t>0.9403,0.0658,0.0087,0.0018</t>
-  </si>
-  <si>
-    <t>0.5536,0.5033,0.0233,0.0062</t>
-  </si>
-  <si>
-    <t>0.9604,0.0158,0.0027,0.0051</t>
-  </si>
-  <si>
-    <t>0.7967,0.2726,0.0185,0.0030</t>
-  </si>
-  <si>
-    <t>0.9390,0.0086,0.0056,0.0227</t>
-  </si>
-  <si>
-    <t>0.1922,0.0164,0.0049,0.8909</t>
-  </si>
-  <si>
-    <t>0.9578,0.0128,0.0022,0.0098</t>
-  </si>
-  <si>
-    <t>0.0065,0.0910,0.9584,0.0259</t>
-  </si>
-  <si>
-    <t>0.7839,0.0004,0.0132,0.1398</t>
-  </si>
-  <si>
-    <t>0.8567,0.0020,0.0081,0.1191</t>
-  </si>
-  <si>
-    <t>0.7602,0.1629,0.0772,0.0081</t>
-  </si>
-  <si>
-    <t>0.8592,0.1331,0.0113,0.0051</t>
-  </si>
-  <si>
-    <t>0.9177,0.0341,0.0526,0.0023</t>
-  </si>
-  <si>
-    <t>0.0678,0.8873,0.0182,0.0304</t>
-  </si>
-  <si>
-    <t>0.7522,0.1541,0.1210,0.0187</t>
-  </si>
-  <si>
-    <t>0.8326,0.0983,0.0213,0.0285</t>
-  </si>
-  <si>
-    <t>0.9913,0.0029,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9460,0.0660,0.0024,0.0022</t>
-  </si>
-  <si>
-    <t>0.9231,0.0617,0.0310,0.0076</t>
-  </si>
-  <si>
-    <t>0.9649,0.0135,0.0058,0.0078</t>
-  </si>
-  <si>
-    <t>0.9479,0.0128,0.0149,0.0102</t>
-  </si>
-  <si>
-    <t>0.9752,0.0083,0.0114,0.0031</t>
-  </si>
-  <si>
-    <t>0.9747,0.0052,0.0091,0.0040</t>
-  </si>
-  <si>
-    <t>0.9732,0.0061,0.0050,0.0041</t>
-  </si>
-  <si>
-    <t>0.5539,0.3532,0.0041,0.0418</t>
-  </si>
-  <si>
-    <t>0.7365,0.3569,0.0070,0.0054</t>
-  </si>
-  <si>
-    <t>0.7290,0.3210,0.0148,0.0043</t>
-  </si>
-  <si>
-    <t>0.2396,0.0831,0.7755,0.0121</t>
-  </si>
-  <si>
-    <t>0.9537,0.0592,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.9247,0.0428,0.0063,0.0094</t>
-  </si>
-  <si>
-    <t>0.9003,0.1785,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9551,0.0400,0.0057,0.0030</t>
-  </si>
-  <si>
-    <t>0.0067,0.0698,0.9875,0.0004</t>
-  </si>
-  <si>
-    <t>0.9540,0.0338,0.0042,0.0035</t>
-  </si>
-  <si>
-    <t>0.0071,0.0030,0.9930,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.2110,0.9509,0.0169</t>
-  </si>
-  <si>
-    <t>0.1060,0.0047,0.9106,0.0079</t>
-  </si>
-  <si>
-    <t>0.0089,0.1296,0.9727,0.0026</t>
-  </si>
-  <si>
-    <t>0.0121,0.0100,0.9782,0.0023</t>
-  </si>
-  <si>
-    <t>0.0033,0.0002,0.9955,0.0006</t>
-  </si>
-  <si>
-    <t>0.0128,0.0036,0.9897,0.0005</t>
-  </si>
-  <si>
-    <t>0.4526,0.1048,0.4565,0.0124</t>
-  </si>
-  <si>
-    <t>0.3441,0.1750,0.5269,0.0279</t>
-  </si>
-  <si>
-    <t>0.3620,0.3133,0.3112,0.0747</t>
-  </si>
-  <si>
-    <t>0.1431,0.0441,0.8112,0.0131</t>
-  </si>
-  <si>
-    <t>0.3228,0.2322,0.4452,0.0108</t>
-  </si>
-  <si>
-    <t>0.5181,0.0390,0.5555,0.0127</t>
-  </si>
-  <si>
-    <t>0.5101,0.1779,0.3805,0.0318</t>
-  </si>
-  <si>
-    <t>0.2808,0.2638,0.4301,0.0187</t>
-  </si>
-  <si>
-    <t>0.8151,0.2526,0.0131,0.0046</t>
-  </si>
-  <si>
-    <t>0.5634,0.5746,0.0037,0.0008</t>
-  </si>
-  <si>
-    <t>0.8605,0.2296,0.0047,0.0013</t>
-  </si>
-  <si>
-    <t>0.9281,0.0704,0.0255,0.0040</t>
-  </si>
-  <si>
-    <t>0.9161,0.1213,0.0066,0.0012</t>
-  </si>
-  <si>
-    <t>0.6363,0.0445,0.1941,0.1283</t>
-  </si>
-  <si>
-    <t>0.8449,0.0043,0.1587,0.0096</t>
-  </si>
-  <si>
-    <t>0.5304,0.0218,0.0464,0.4643</t>
-  </si>
-  <si>
-    <t>0.3438,0.0382,0.6513,0.0319</t>
-  </si>
-  <si>
-    <t>0.5605,0.0338,0.4645,0.0440</t>
-  </si>
-  <si>
-    <t>0.0528,0.0358,0.8650,0.0649</t>
-  </si>
-  <si>
-    <t>0.0241,0.1527,0.8643,0.0696</t>
-  </si>
-  <si>
-    <t>0.0398,0.1246,0.9207,0.0084</t>
-  </si>
-  <si>
-    <t>0.0780,0.0207,0.9384,0.0033</t>
-  </si>
-  <si>
-    <t>0.0028,0.3258,0.9109,0.0068</t>
-  </si>
-  <si>
-    <t>0.9870,0.0039,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.9808,0.0331,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9764,0.0074,0.0006,0.0029</t>
-  </si>
-  <si>
-    <t>0.9717,0.0195,0.0059,0.0015</t>
-  </si>
-  <si>
-    <t>0.9818,0.0143,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.9738,0.0178,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9495,0.0614,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.9870,0.0045,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.0765,0.0099,0.9501,0.0010</t>
-  </si>
-  <si>
-    <t>0.2168,0.2052,0.6104,0.0058</t>
-  </si>
-  <si>
-    <t>0.8123,0.0590,0.0506,0.0717</t>
-  </si>
-  <si>
-    <t>0.0032,0.0138,0.9905,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.0025,0.9947,0.0013</t>
-  </si>
-  <si>
-    <t>0.0059,0.0154,0.9899,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9984,0.0021</t>
-  </si>
-  <si>
-    <t>0.0211,0.0354,0.9527,0.0008</t>
-  </si>
-  <si>
-    <t>0.0092,0.0203,0.9870,0.0013</t>
-  </si>
-  <si>
-    <t>0.0135,0.0734,0.9501,0.0005</t>
-  </si>
-  <si>
-    <t>0.0483,0.3658,0.6022,0.0049</t>
-  </si>
-  <si>
-    <t>0.6350,0.0132,0.4095,0.0190</t>
-  </si>
-  <si>
-    <t>0.5211,0.0120,0.4942,0.0572</t>
-  </si>
-  <si>
-    <t>0.7299,0.0129,0.2012,0.0456</t>
-  </si>
-  <si>
-    <t>0.9803,0.0071,0.0019,0.0030</t>
-  </si>
-  <si>
-    <t>0.9716,0.0182,0.0066,0.0019</t>
-  </si>
-  <si>
-    <t>0.9855,0.0106,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.9829,0.0129,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.9664,0.0183,0.0089,0.0025</t>
-  </si>
-  <si>
-    <t>0.9839,0.0130,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9880,0.0049,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9821,0.0082,0.0020,0.0022</t>
-  </si>
-  <si>
-    <t>0.0760,0.1716,0.7150,0.0028</t>
-  </si>
-  <si>
-    <t>0.0003,0.0174,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0070,0.0084,0.9861,0.0017</t>
-  </si>
-  <si>
-    <t>0.0672,0.2602,0.6306,0.0059</t>
-  </si>
-  <si>
-    <t>0.0006,0.0021,0.9909,0.0085</t>
-  </si>
-  <si>
-    <t>0.1959,0.1588,0.4926,0.2821</t>
-  </si>
-  <si>
-    <t>0.3024,0.0476,0.7022,0.0368</t>
-  </si>
-  <si>
-    <t>0.0156,0.0207,0.9054,0.0700</t>
-  </si>
-  <si>
-    <t>0.7487,0.0042,0.0065,0.3146</t>
-  </si>
-  <si>
-    <t>0.0066,0.2377,0.0072,0.9812</t>
-  </si>
-  <si>
-    <t>0.0842,0.0051,0.0014,0.9724</t>
-  </si>
-  <si>
-    <t>0.0059,0.0005,0.0056,0.9934</t>
-  </si>
-  <si>
-    <t>0.0065,0.0002,0.0003,0.9975</t>
-  </si>
-  <si>
-    <t>0.5993,0.1989,0.1057,0.1560</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7913,0.0247,0.0399,0.1095</t>
+  </si>
+  <si>
+    <t>0.0102,0.0015,0.0015,0.9945</t>
+  </si>
+  <si>
+    <t>0.3042,0.0148,0.0023,0.8016</t>
+  </si>
+  <si>
+    <t>0.2350,0.0024,0.0066,0.8848</t>
+  </si>
+  <si>
+    <t>0.9955,0.0014,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9898,0.0029,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9747,0.0178,0.0086,0.0013</t>
+  </si>
+  <si>
+    <t>0.9876,0.0032,0.0025,0.0017</t>
+  </si>
+  <si>
+    <t>0.8898,0.1466,0.0077,0.0020</t>
+  </si>
+  <si>
+    <t>0.9911,0.0019,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9925,0.0019,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9937,0.0017,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.4088,0.2459,0.3650,0.1776</t>
+  </si>
+  <si>
+    <t>0.2821,0.0558,0.7121,0.0091</t>
+  </si>
+  <si>
+    <t>0.1961,0.0112,0.8720,0.0009</t>
+  </si>
+  <si>
+    <t>0.3041,0.0119,0.8174,0.0025</t>
+  </si>
+  <si>
+    <t>0.6888,0.0311,0.3432,0.0179</t>
+  </si>
+  <si>
+    <t>0.0268,0.9698,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.0210,0.9768,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.5988,0.5445,0.0067,0.0018</t>
+  </si>
+  <si>
+    <t>0.3877,0.7819,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.9956,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.5786,0.0090,0.1546,0.1882</t>
+  </si>
+  <si>
+    <t>0.4464,0.0460,0.4545,0.0907</t>
+  </si>
+  <si>
+    <t>0.0161,0.0028,0.9311,0.0501</t>
+  </si>
+  <si>
+    <t>0.0488,0.0127,0.9418,0.0045</t>
+  </si>
+  <si>
+    <t>0.2561,0.0061,0.7726,0.0258</t>
+  </si>
+  <si>
+    <t>0.1234,0.0207,0.8357,0.0310</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9904,0.0216</t>
+  </si>
+  <si>
+    <t>0.1364,0.8884,0.0033,0.0027</t>
+  </si>
+  <si>
+    <t>0.4399,0.1837,0.4736,0.0540</t>
+  </si>
+  <si>
+    <t>0.0021,0.0035,0.9932,0.0016</t>
+  </si>
+  <si>
+    <t>0.1244,0.3438,0.3982,0.0009</t>
+  </si>
+  <si>
+    <t>0.8231,0.1143,0.0131,0.0270</t>
+  </si>
+  <si>
+    <t>0.0694,0.0697,0.9129,0.0034</t>
+  </si>
+  <si>
+    <t>0.6493,0.5065,0.0125,0.0018</t>
+  </si>
+  <si>
+    <t>0.0109,0.9668,0.1030,0.0014</t>
+  </si>
+  <si>
+    <t>0.0202,0.8543,0.1796,0.0627</t>
+  </si>
+  <si>
+    <t>0.0860,0.0090,0.8929,0.0238</t>
+  </si>
+  <si>
+    <t>0.0922,0.3290,0.7392,0.0138</t>
+  </si>
+  <si>
+    <t>0.2997,0.0130,0.5428,0.1161</t>
+  </si>
+  <si>
+    <t>0.0175,0.0790,0.9501,0.0010</t>
+  </si>
+  <si>
+    <t>0.0416,0.8925,0.0907,0.0018</t>
+  </si>
+  <si>
+    <t>0.0582,0.1323,0.7813,0.0365</t>
+  </si>
+  <si>
+    <t>0.0744,0.5924,0.0956,0.6189</t>
+  </si>
+  <si>
+    <t>0.0160,0.9493,0.0639,0.0057</t>
+  </si>
+  <si>
+    <t>0.0099,0.9638,0.0574,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9961,0.0161,0.0039</t>
+  </si>
+  <si>
+    <t>0.0031,0.4445,0.9134,0.0058</t>
+  </si>
+  <si>
+    <t>0.0019,0.1255,0.9840,0.0012</t>
+  </si>
+  <si>
+    <t>0.0500,0.0146,0.9455,0.0042</t>
+  </si>
+  <si>
+    <t>0.0764,0.0049,0.9579,0.0014</t>
+  </si>
+  <si>
+    <t>0.0106,0.0040,0.9878,0.0009</t>
+  </si>
+  <si>
+    <t>0.0048,0.0134,0.9830,0.0023</t>
+  </si>
+  <si>
+    <t>0.9220,0.1069,0.0077,0.0009</t>
+  </si>
+  <si>
+    <t>0.9329,0.0485,0.0131,0.0083</t>
+  </si>
+  <si>
+    <t>0.9720,0.0097,0.0012,0.0050</t>
+  </si>
+  <si>
+    <t>0.0046,0.0338,0.9743,0.0127</t>
+  </si>
+  <si>
+    <t>0.9649,0.0237,0.0058,0.0020</t>
+  </si>
+  <si>
+    <t>0.9900,0.0060,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.8931,0.1516,0.0095,0.0012</t>
+  </si>
+  <si>
+    <t>0.0007,0.8066,0.9732,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.2345,0.9663,0.0040</t>
+  </si>
+  <si>
+    <t>0.0789,0.0610,0.8930,0.0181</t>
+  </si>
+  <si>
+    <t>0.0003,0.9678,0.9031,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0050,0.9875,0.0045</t>
+  </si>
+  <si>
+    <t>0.1082,0.8747,0.0169,0.0013</t>
+  </si>
+  <si>
+    <t>0.0034,0.9840,0.0190,0.0001</t>
+  </si>
+  <si>
+    <t>0.8545,0.0132,0.2152,0.0068</t>
+  </si>
+  <si>
+    <t>0.6672,0.2742,0.0558,0.0335</t>
+  </si>
+  <si>
+    <t>0.0118,0.0308,0.9694,0.0010</t>
+  </si>
+  <si>
+    <t>0.0062,0.7710,0.7558,0.0010</t>
+  </si>
+  <si>
+    <t>0.0071,0.5953,0.8796,0.0012</t>
+  </si>
+  <si>
+    <t>0.0026,0.9676,0.1394,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9771,0.2587,0.0001</t>
+  </si>
+  <si>
+    <t>0.0502,0.0012,0.0102,0.9674</t>
+  </si>
+  <si>
+    <t>0.0019,0.0060,0.0008,0.9980</t>
+  </si>
+  <si>
+    <t>0.0057,0.0008,0.0003,0.9975</t>
+  </si>
+  <si>
+    <t>0.0167,0.0010,0.0024,0.9909</t>
+  </si>
+  <si>
+    <t>0.0170,0.0032,0.0113,0.9855</t>
+  </si>
+  <si>
+    <t>0.0133,0.0101,0.0037,0.9901</t>
+  </si>
+  <si>
+    <t>0.0002,0.9569,0.9169,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.8697,0.9638,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.3548,0.9339,0.0032</t>
+  </si>
+  <si>
+    <t>0.0094,0.1338,0.9418,0.0065</t>
+  </si>
+  <si>
+    <t>0.0059,0.9306,0.1982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9295,0.7076,0.0001</t>
+  </si>
+  <si>
+    <t>0.9511,0.0394,0.0148,0.0044</t>
+  </si>
+  <si>
+    <t>0.9688,0.0237,0.0129,0.0009</t>
+  </si>
+  <si>
+    <t>0.9802,0.0312,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9867,0.0034,0.0025,0.0025</t>
+  </si>
+  <si>
+    <t>0.9753,0.0174,0.0035,0.0020</t>
+  </si>
+  <si>
+    <t>0.9942,0.0026,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9758,0.0219,0.0032,0.0009</t>
+  </si>
+  <si>
+    <t>0.9781,0.0120,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.9953,0.0009,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9935,0.0023,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9918,0.0009,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9947,0.0007,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9927,0.0039,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0048,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9923,0.0009,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9824,0.0063,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.0119,0.0016,0.9654,0.0279</t>
+  </si>
+  <si>
+    <t>0.0070,0.0062,0.9806,0.0039</t>
+  </si>
+  <si>
+    <t>0.6829,0.0062,0.3632,0.0241</t>
+  </si>
+  <si>
+    <t>0.3809,0.0019,0.8360,0.0012</t>
+  </si>
+  <si>
+    <t>0.0502,0.9461,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.0220,0.9735,0.0029,0.0009</t>
+  </si>
+  <si>
+    <t>0.0158,0.9688,0.0020,0.0064</t>
+  </si>
+  <si>
+    <t>0.0627,0.9255,0.0010,0.0056</t>
+  </si>
+  <si>
+    <t>0.1428,0.8379,0.0025,0.0109</t>
+  </si>
+  <si>
+    <t>0.0208,0.9754,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.8225,0.2856,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.5835,0.2874,0.1551,0.0264</t>
+  </si>
+  <si>
+    <t>0.4520,0.0313,0.6017,0.0095</t>
+  </si>
+  <si>
+    <t>0.0887,0.7856,0.0821,0.0323</t>
+  </si>
+  <si>
+    <t>0.5239,0.1192,0.4054,0.0535</t>
+  </si>
+  <si>
+    <t>0.4494,0.1018,0.2913,0.3377</t>
+  </si>
+  <si>
+    <t>0.0020,0.9848,0.0398,0.0058</t>
+  </si>
+  <si>
+    <t>0.0026,0.9866,0.0213,0.0012</t>
+  </si>
+  <si>
+    <t>0.0161,0.9548,0.0187,0.0171</t>
+  </si>
+  <si>
+    <t>0.0001,0.9794,0.7478,0.0004</t>
+  </si>
+  <si>
+    <t>0.0339,0.9537,0.0499,0.0019</t>
+  </si>
+  <si>
+    <t>0.8786,0.1358,0.0221,0.0044</t>
+  </si>
+  <si>
+    <t>0.1793,0.8164,0.0046,0.0180</t>
+  </si>
+  <si>
+    <t>0.9687,0.0262,0.0123,0.0012</t>
+  </si>
+  <si>
+    <t>0.9873,0.0021,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9359,0.0347,0.0207,0.0058</t>
+  </si>
+  <si>
+    <t>0.9536,0.0302,0.0067,0.0041</t>
+  </si>
+  <si>
+    <t>0.9889,0.0010,0.0009,0.0033</t>
+  </si>
+  <si>
+    <t>0.9628,0.0602,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9788,0.0061,0.0100,0.0017</t>
+  </si>
+  <si>
+    <t>0.9760,0.0061,0.0134,0.0021</t>
+  </si>
+  <si>
+    <t>0.0007,0.8414,0.9477,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.6533,0.7465,0.0004</t>
+  </si>
+  <si>
+    <t>0.0114,0.1912,0.9433,0.0008</t>
+  </si>
+  <si>
+    <t>0.0707,0.0617,0.8559,0.0041</t>
+  </si>
+  <si>
+    <t>0.6006,0.0671,0.2955,0.0968</t>
+  </si>
+  <si>
+    <t>0.4860,0.1179,0.1080,0.3914</t>
+  </si>
+  <si>
+    <t>0.6057,0.0043,0.5866,0.0069</t>
+  </si>
+  <si>
+    <t>0.6699,0.0140,0.3548,0.0310</t>
+  </si>
+  <si>
+    <t>0.3533,0.0016,0.0029,0.8220</t>
+  </si>
+  <si>
+    <t>0.0007,0.0039,0.0019,0.9987</t>
+  </si>
+  <si>
+    <t>0.0016,0.0153,0.0014,0.9975</t>
+  </si>
+  <si>
+    <t>0.0219,0.0009,0.0009,0.9924</t>
+  </si>
+  <si>
+    <t>0.0035,0.7529,0.6789,0.0003</t>
+  </si>
+  <si>
+    <t>0.9283,0.0940,0.0027,0.0021</t>
+  </si>
+  <si>
+    <t>0.6024,0.3918,0.0311,0.0033</t>
+  </si>
+  <si>
+    <t>0.9284,0.0870,0.0018,0.0027</t>
+  </si>
+  <si>
+    <t>0.6579,0.4480,0.0114,0.0050</t>
+  </si>
+  <si>
+    <t>0.9460,0.0275,0.0138,0.0050</t>
+  </si>
+  <si>
+    <t>0.2618,0.0016,0.0153,0.8149</t>
+  </si>
+  <si>
+    <t>0.9656,0.0059,0.0016,0.0113</t>
+  </si>
+  <si>
+    <t>0.0003,0.0445,0.9774,0.0560</t>
+  </si>
+  <si>
+    <t>0.8022,0.0030,0.0053,0.1992</t>
+  </si>
+  <si>
+    <t>0.8519,0.0215,0.0761,0.0380</t>
+  </si>
+  <si>
+    <t>0.7424,0.1803,0.0116,0.0292</t>
+  </si>
+  <si>
+    <t>0.7448,0.2544,0.0294,0.0140</t>
+  </si>
+  <si>
+    <t>0.7580,0.1925,0.0811,0.0124</t>
+  </si>
+  <si>
+    <t>0.4989,0.4620,0.0263,0.0204</t>
+  </si>
+  <si>
+    <t>0.7777,0.0685,0.1961,0.0056</t>
+  </si>
+  <si>
+    <t>0.8173,0.0899,0.0518,0.0241</t>
+  </si>
+  <si>
+    <t>0.9871,0.0024,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.9509,0.0150,0.0100,0.0108</t>
+  </si>
+  <si>
+    <t>0.9766,0.0155,0.0011,0.0023</t>
+  </si>
+  <si>
+    <t>0.9729,0.0054,0.0076,0.0056</t>
+  </si>
+  <si>
+    <t>0.9699,0.0126,0.0071,0.0037</t>
+  </si>
+  <si>
+    <t>0.9235,0.0479,0.0414,0.0049</t>
+  </si>
+  <si>
+    <t>0.9863,0.0017,0.0005,0.0043</t>
+  </si>
+  <si>
+    <t>0.9662,0.0023,0.0001,0.0177</t>
+  </si>
+  <si>
+    <t>0.6256,0.3834,0.0122,0.0242</t>
+  </si>
+  <si>
+    <t>0.6641,0.4596,0.0040,0.0033</t>
+  </si>
+  <si>
+    <t>0.8029,0.3513,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.7707,0.1245,0.1229,0.0210</t>
+  </si>
+  <si>
+    <t>0.4536,0.5617,0.0090,0.0145</t>
+  </si>
+  <si>
+    <t>0.9182,0.0550,0.0065,0.0076</t>
+  </si>
+  <si>
+    <t>0.9574,0.0443,0.0099,0.0004</t>
+  </si>
+  <si>
+    <t>0.9284,0.0418,0.0060,0.0102</t>
+  </si>
+  <si>
+    <t>0.0007,0.0130,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.9052,0.1059,0.0093,0.0037</t>
+  </si>
+  <si>
+    <t>0.0005,0.0038,0.9958,0.0015</t>
+  </si>
+  <si>
+    <t>0.0100,0.1277,0.9669,0.0018</t>
+  </si>
+  <si>
+    <t>0.0603,0.0052,0.9329,0.0086</t>
+  </si>
+  <si>
+    <t>0.0084,0.0295,0.9671,0.0071</t>
+  </si>
+  <si>
+    <t>0.0141,0.0190,0.9760,0.0012</t>
+  </si>
+  <si>
+    <t>0.0242,0.0029,0.9827,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.0042,0.9914,0.0023</t>
+  </si>
+  <si>
+    <t>0.3764,0.1730,0.4386,0.0557</t>
+  </si>
+  <si>
+    <t>0.2859,0.0175,0.7985,0.0083</t>
+  </si>
+  <si>
+    <t>0.3886,0.2145,0.3827,0.0160</t>
+  </si>
+  <si>
+    <t>0.0935,0.0391,0.8667,0.0022</t>
+  </si>
+  <si>
+    <t>0.5474,0.2334,0.2654,0.0164</t>
+  </si>
+  <si>
+    <t>0.2178,0.0846,0.7300,0.0063</t>
+  </si>
+  <si>
+    <t>0.4252,0.2047,0.4770,0.0289</t>
+  </si>
+  <si>
+    <t>0.5092,0.0250,0.5946,0.0060</t>
+  </si>
+  <si>
+    <t>0.7875,0.4110,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.7286,0.4718,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.8926,0.1130,0.0242,0.0037</t>
+  </si>
+  <si>
+    <t>0.9800,0.0206,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.3443,0.7886,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.6067,0.1341,0.2588,0.1100</t>
+  </si>
+  <si>
+    <t>0.4993,0.0086,0.5857,0.0268</t>
+  </si>
+  <si>
+    <t>0.4011,0.0501,0.4649,0.1736</t>
+  </si>
+  <si>
+    <t>0.5321,0.0144,0.6084,0.0064</t>
+  </si>
+  <si>
+    <t>0.2387,0.0184,0.8091,0.0107</t>
+  </si>
+  <si>
+    <t>0.0009,0.0129,0.9469,0.1943</t>
+  </si>
+  <si>
+    <t>0.0423,0.0801,0.9103,0.0095</t>
+  </si>
+  <si>
+    <t>0.0070,0.1026,0.9692,0.0038</t>
+  </si>
+  <si>
+    <t>0.0318,0.2152,0.9072,0.0103</t>
+  </si>
+  <si>
+    <t>0.0022,0.0265,0.9759,0.0054</t>
+  </si>
+  <si>
+    <t>0.9837,0.0076,0.0021,0.0018</t>
+  </si>
+  <si>
+    <t>0.9669,0.0172,0.0129,0.0022</t>
+  </si>
+  <si>
+    <t>0.9760,0.0279,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9900,0.0111,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9728,0.0174,0.0057,0.0022</t>
+  </si>
+  <si>
+    <t>0.9836,0.0066,0.0020,0.0021</t>
+  </si>
+  <si>
+    <t>0.9829,0.0165,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9835,0.0094,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.0330,0.0088,0.9747,0.0013</t>
+  </si>
+  <si>
+    <t>0.4064,0.1067,0.5876,0.0078</t>
+  </si>
+  <si>
+    <t>0.9376,0.0131,0.0199,0.0120</t>
+  </si>
+  <si>
+    <t>0.0398,0.0393,0.9336,0.0075</t>
+  </si>
+  <si>
+    <t>0.0004,0.0031,0.9965,0.0008</t>
+  </si>
+  <si>
+    <t>0.0388,0.0649,0.9129,0.0023</t>
+  </si>
+  <si>
+    <t>0.0001,0.0063,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0407,0.1926,0.7739,0.0109</t>
+  </si>
+  <si>
+    <t>0.0005,0.0038,0.9969,0.0006</t>
+  </si>
+  <si>
+    <t>0.0025,0.0073,0.9896,0.0031</t>
+  </si>
+  <si>
+    <t>0.1522,0.0794,0.7076,0.0106</t>
+  </si>
+  <si>
+    <t>0.6840,0.0046,0.4819,0.0067</t>
+  </si>
+  <si>
+    <t>0.1485,0.0044,0.8486,0.0260</t>
+  </si>
+  <si>
+    <t>0.6189,0.0107,0.1734,0.1802</t>
+  </si>
+  <si>
+    <t>0.9526,0.0441,0.0121,0.0024</t>
+  </si>
+  <si>
+    <t>0.9781,0.0190,0.0037,0.0007</t>
+  </si>
+  <si>
+    <t>0.9893,0.0035,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9806,0.0159,0.0065,0.0006</t>
+  </si>
+  <si>
+    <t>0.9776,0.0036,0.0006,0.0058</t>
+  </si>
+  <si>
+    <t>0.9507,0.0521,0.0072,0.0014</t>
+  </si>
+  <si>
+    <t>0.9805,0.0208,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9773,0.0182,0.0026,0.0020</t>
+  </si>
+  <si>
+    <t>0.0169,0.0326,0.9626,0.0042</t>
+  </si>
+  <si>
+    <t>0.0027,0.0118,0.9899,0.0011</t>
+  </si>
+  <si>
+    <t>0.0353,0.0868,0.9098,0.0067</t>
+  </si>
+  <si>
+    <t>0.0593,0.0055,0.9540,0.0011</t>
+  </si>
+  <si>
+    <t>0.0072,0.0051,0.9861,0.0019</t>
+  </si>
+  <si>
+    <t>0.0891,0.0248,0.8286,0.0594</t>
+  </si>
+  <si>
+    <t>0.0732,0.0297,0.8908,0.0214</t>
+  </si>
+  <si>
+    <t>0.0256,0.4598,0.8281,0.0267</t>
+  </si>
+  <si>
+    <t>0.7785,0.0002,0.0008,0.3931</t>
+  </si>
+  <si>
+    <t>0.0042,0.0763,0.0029,0.9924</t>
+  </si>
+  <si>
+    <t>0.0084,0.0007,0.0008,0.9965</t>
+  </si>
+  <si>
+    <t>0.0080,0.0001,0.0003,0.9977</t>
+  </si>
+  <si>
+    <t>0.0169,0.0001,0.0004,0.9954</t>
+  </si>
+  <si>
+    <t>0.3862,0.2866,0.0315,0.2740</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4415,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4670,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
